--- a/files_result_13.07.2025/Поставщики комплектующих.xlsx
+++ b/files_result_13.07.2025/Поставщики комплектующих.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20658F16-500D-46E4-A916-49153DFD478C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646123B-4741-4768-B7BB-6C0FA7F7C35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
